--- a/SeleniumProject/src/main/resources/excel.xlsx
+++ b/SeleniumProject/src/main/resources/excel.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11430" windowHeight="3645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11430" windowHeight="3075" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="news" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
+  <oleSize ref="A1:K9"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>admin</t>
   </si>
@@ -32,6 +33,9 @@
   </si>
   <si>
     <t>asweed</t>
+  </si>
+  <si>
+    <t>19 yr old murdered</t>
   </si>
 </sst>
 </file>
@@ -379,4 +383,22 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>